--- a/docs/WiseTrader_Feature_Log.xlsx
+++ b/docs/WiseTrader_Feature_Log.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="5" customWidth="1" style="21" min="1" max="1"/>
@@ -1931,12 +1931,271 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
+          <t>Built and validated - Console/wfe_score.py</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Reimplement the scoring math (not the MQL5/CCanvas UI) in Python against existing regression_history.csv + journal equity series; score A2_tuned's primary-window vs OOS split retroactively as a first real test of the tool || REAL EXAMPLE 2026-07-23: E9_eur_tuned (5 toggles combined, all tuned on the same 2025H2 window) hit exactly the failure mode this tool detects - in-sample PF 1.53-1.60, OOS PF 0.81. Would have caught this before wasting a model-4 run. || BUILT 2026-08-06: Console/wfe_score.py reimplements ComputeWFE() (WFE=SR_OOS/SR_IS with the non-positive and near-zero-IS guards) against Sharpe values already in results/regression_history.csv - no MQL5/EA change, no per-bar equity export needed. First real test on 4 known campaign pairs: A2_tuned PASS (WFE 1.18), W1_volregime_on PASS (WFE 1.06, confirms F55 genuinely generalized even though it wasn't better than baseline - WFE answers 'did it overfit', not 'is it the best option', two different questions), E9_eur_tuned FAIL (WFE -0.68), S5_silver_tuned FAIL (WFE -0.46) - correctly flags both known overfit collapses. Tool works as intended. Next: run it as a standard step whenever a config gets both an IS and OOS backtest, instead of eyeballing the PF/expectancy comparison by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>F52</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>RSI momentum confluence score (sustained-pressure window, 14+ bars)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Structure/BOS-CHoCH asks whether price broke a level; momentum asks whether the move is actually accelerating or running out of steam over a longer smoothed window than the 3-4 bar swing-confirmation logic already uses - a genuinely different signal family, not a duplicate.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>User-observed gap: EA not acting on visible chart moves early (2026-07-24 XAUUSD/GBPUSD demo journal, relVol vetoes) prompted a review of movement-signal alternatives beyond bar-counting</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Rejected (M15) / Candidate (M30, unvalidated)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>T-series ablation (tests/configs/T0_baseline_m30, T0_baseline_h1, T1_momentum_m15/m30/h1) vs A2_tuned at M15/M30/H1, XAUUSD, model 1 first; judge by expectancy+PF n&gt;=30, then model 4 + OOS before considering live. First of F52-F57 movement-signal candidate series. || RESULT 2026-07-28 (XAUUSD, 2026.01.01-2026.07.08, model 1): M15 momentum ON vs A2_tuned OFF: PF 1.44-&gt;1.19, exp $8.43-&gt;$4.01, net $893-&gt;$461, Sharpe 5.34-&gt;2.19, n=106-&gt;115 - REJECTED as default, the additive-only score bonus (never subtracts on misalignment) just admits more marginal trades past the 0.55 threshold on an already-tuned config, diluting quality. M30 momentum ON vs M30 baseline OFF: flipped a losing config to marginally profitable (PF 0.86-&gt;1.14, exp -$3.66-&gt;$3.29, net -$205-&gt;$211) but M30 itself is unvalidated for this symbol/strategy (baseline alone loses money) and n=56-64 is thin - not enough evidence to pursue further without a dedicated M30 campaign, which is out of scope unless M30 becomes a real deployment candidate on its own merits first. H1 configs untested (MT5 tester history-cache build error, deferred).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>F53</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OLS trend-slope confluence score (linear regression over 20-50 bars)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fits a line over the last N closes; slope sign agreeing with trade direction (gated on R^2 so noise can't count as trend) catches grinding, low-volatility trends that never produce a clean structure swing break - structure's own blind spot, cheap to compute incrementally.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Movement-signal candidate series (F52-F57), same origin as F52</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Rejected (marginal, worse Sharpe)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>tests/configs/U1_regression_on vs A2_tuned, XAUUSD M15, 2026.01.01-2026.07.08, model 1 first; judge by expectancy+PF n&gt;=30, then model 4 + OOS before considering live. || RESULT 2026-07-28 (XAUUSD, 2026.01.01-2026.07.08, model 1): U1_regression_on vs A2_tuned: net $893-&gt;$948 (+6%), exp $8.43-&gt;$8.62 (+2%), PF unchanged 1.44, but Sharpe 5.34-&gt;4.56 (-15%) and max DD 2.94%-&gt;3.01%, n=106-&gt;110. Marginal raw-return gain offset by worse risk-adjusted quality - same pattern the project has already learned not to trust in-sample (see F51/E9/S5 overfit lesson). Not pursued to model 4/OOS; REJECTED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>F54</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ehlers CycleTurn score weight sweep (0.20 -&gt; 0.30/0.40)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CycleTurn is frequency-domain (cycle phase), not bar-counting like most of the rest of the scorer; was hardcoded at 0.20 since v1.8's rebalance - never revisited since. Testing whether it's underweighted relative to its information content.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Movement-signal candidate series (F52-F57), same origin as F52/F53</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rejected (zero effect)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>tests/configs/V1_cycleweight_030, V2_cycleweight_040 vs A2_tuned (0.20), XAUUSD M15, 2026.01.01-2026.07.08, model 1. || RESULT 2026-07-28 (XAUUSD, 2026.01.01-2026.07.08, model 1): V1 (weight 0.30) and V2 (weight 0.40) produced results IDENTICAL to A2_tuned (weight 0.20) down to the cent - net $893.38, PF 1.44, n=106, Sharpe 5.34, all three runs. Cause: score only gates entry via InpMinScore=0.55 (magnitude above threshold is unused elsewhere); no CycleTurn-aligned setup in this window sat in the band the weight change could flip. Underweighting hypothesis disproven, not just unsupported - REJECTED, no further sweep warranted on this window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>F55</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ATR14/ATR100 volatility-expansion confluence score (directionless)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Volatility expanding after a squeeze is a movement signal in its own right, independent of where swing pivots fall; reuses the same ratio family Risk.mqh already computes for sizing but as a separate scored signal input, not a sizing input.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Movement-signal candidate series (F52-F57), same origin as F52/F53/F54</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Gauntlet complete - NOT promoted (parity OOS)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>tests/configs/W1_volregime_on vs A2_tuned, XAUUSD M15, 2026.01.01-2026.07.08, model 1. || RESULT 2026-07-28 (XAUUSD, 2026.01.01-2026.07.08, model 1): W1_volregime_on vs A2_tuned: net $893-&gt;$1026 (+15%), PF 1.44-&gt;1.52, exp $8.43-&gt;$9.50 (+13%), win rate 67.9%-&gt;68.5%, avg loss -$59-&gt;-$58, Sharpe 5.34-&gt;5.37 (held, didn't degrade), n=106-&gt;108, DD roughly flat (2.94%-&gt;3.01%). Strongest single-window result of the F52-F57 series so far - but per the E9_eur_tuned lesson (looked this good on model 1 AND model 4 in-sample, then PF 0.81 OOS), NOT to be trusted without model 4 confirm + OOS on the untouched 2025H2 window before any live consideration. Next: model 4 confirm, then OOS. || GAUNTLET 2026-07-30/31: model 4 confirm (in-sample) held the edge (PF 1.39-&gt;1.47, exp $7.49-&gt;$8.65 vs A2_tuned's own model-4 number) - not a fill-model artifact. But OOS (2025H2, model 4) came back at PARITY with A2_tuned's own OOS result (PF 1.51 vs 1.54, DD 5.28% vs 4.8%), not a clear win. Unlike E9_eur_tuned this doesn't collapse OOS - it's a real, reproducible in-sample edge that just doesn't clearly beat the existing baseline once OOS is priced in. VERDICT: not promoted to default; kept as a validated, documented candidate (InpUseVolRegime=false) for future reconsideration rather than a flat rejection. || 2026-08-06: user decision - demo stays on A2_tuned, F55 NOT deployed despite being the strongest candidate of the series, since OOS was only at parity (not a clear win) and the demo clock had just been reset (see [[wise-trader-demo-tracking]]) for an unrelated data-integrity issue. Available to revisit if a future campaign strengthens the OOS case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>F56</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Variance-ratio persistence confluence score (Lo-MacKinlay style, directionless)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Tells whether the current regime is trending-persistent (VR&gt;1) or mean-reverting (VR&lt;1) before trusting a bar-based breakout signal at all - a genuinely different question than direction or volatility level. Simpler, equally standard alternative to a literal Hurst exponent for the same question the Feature Engineering Part 9 article raises.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Feature Engineering Part 9 (Structural Break Tests) + movement-signal candidate series (F52-F57)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rejected (confirmed active, net negative)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>tests/configs/X1_persistence_on vs A2_tuned, XAUUSD M15, 2026.01.01-2026.07.08, model 1. || RESULT 2026-07-31 (XAUUSD, 2026.01.01-2026.07.08, model 1): X1_persistence_on vs A2_tuned: net $893-&gt;$790 (-12%), PF 1.44-&gt;1.36, exp $8.43-&gt;$7.18 (-15%), max DD 2.94%-&gt;3.74%, Sharpe 5.34-&gt;4.51 (-16%), n=106-&gt;110. Confirmed genuinely firing (VR= tag present across many setups in the journal, 1.15-1.26+) - real result, same dilution pattern as F52/F53. REJECTED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>F57</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Multi-timeframe (H1) directional agreement confluence score</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Checks whether a higher timeframe (H1 close vs its own EMA50) agrees with the M15 trade direction before scoring it - catches 'M15 broke a level but H1 is still ranging/opposed', a failure mode no amount of extra M15-only signal work (F52-F56) can see, since it's a different timeframe entirely rather than a better read of the same one.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Movement-signal candidate series (F52-F57), same origin as F52-F56 - last in the series</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Inconclusive - deprioritized (tooling)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>tests/configs/Y1_mtf_h1_on vs A2_tuned, XAUUSD M15, 2026.01.01-2026.07.08, model 1. NOTE: may hit the same H1 history-cache error as the earlier H1-InpTF configs since it pulls H1 data internally; open an H1 chart once first if so. || 2026-08-01: first Y1_mtf_h1_on run produced results IDENTICAL to A2_tuned across all 354 evaluated setups (journal has zero 'MTF' tags) - the H1 EMA handle came back INVALID_HANDLE at Init() (secondary-TF handle race, known MT5 tester quirk) and never recovered with no retry logic. Fixed in v2.50: MtfBias() now retries iMA() lazily on every call. Needs a rerun before any real verdict - this measured 'feature never activated,' not 'feature doesn't help.' || 2026-08-06: THIRD attempt (v2.51 diagnostic build) failed outright (no report, 96s) - never produced the instrumented journal data needed to diagnose the original silent-null result. Three attempts (silent null x2, then hard failure) without usable evidence either way. DEPRIORITIZED per user decision 2026-08-06 rather than keep burning test cycles on a tooling issue - not rejected on merit, just unresolved. Revisit only if H1 data access in the tester environment gets sorted out for unrelated reasons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>F58</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Execution cost / slippage cushion analyzer (breakeven cost, cost-scaled PF, win erosion)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Backtests charge optimistic, often-fixed costs; this quantifies exactly how much real-world spread/slippage/commission an edge can absorb before it disappears (cushion = net profit / assumed total cost) and which winners are 'thin' enough to flip to losers under realistic costs - a different failure mode than overfitting (F51/WFE), specifically the backtest-vs-live gap this project has already worried about via the demo forward-test.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Execution Cost and Slippage Sensitivity Analyzer - MQL5 Articles, 2026-07-23</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>Candidate</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Reimplement the scoring math (not the MQL5/CCanvas UI) in Python against existing regression_history.csv + journal equity series; score A2_tuned's primary-window vs OOS split retroactively as a first real test of the tool || REAL EXAMPLE 2026-07-23: E9_eur_tuned (5 toggles combined, all tuned on the same 2025H2 window) hit exactly the failure mode this tool detects - in-sample PF 1.53-1.60, OOS PF 0.81. Would have caught this before wasting a model-4 run.</t>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Reimplement the cost-sensitivity math in Python (same approach as F51) against per-deal data already extractable from tester .htm reports' Deals table or journal ORDER/fill lines - no MQL5 script or EA change needed. Run against A2_tuned's own regression reports first as a first real test of the tool, same as F51's plan.</t>
         </is>
       </c>
     </row>
@@ -1953,7 +2212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" style="21" min="1" max="1"/>
@@ -2217,6 +2476,134 @@
       <c r="F8" s="19" t="inlineStr">
         <is>
           <t>NOT rejected - recommended. This is validation tooling, not a trading signal, so it carries none of the live-trading risk of a strategy candidate. It's a more rigorous version of what the project's own OOS discipline already does by hand (primary window vs OOS window, gate on PF/expectancy/DD); worth reimplementing the scoring math in Python against existing regression_history.csv data as a cheap first step - no MQL5/EA changes needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Building a Hierarchical Market Structure Framework (Prototype) in MQL5 Using Modular Architecture and Event-Driven Design</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MT5 Library</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Software-architecture exercise (not a strategy): modular, event-driven BOS/CHoCH framework with explicit INTERNAL (current-TF) vs EXTERNAL (higher-TF) structure classification, a market state machine, event bus, and persistence. Author's own caveat: prototype, trend model and confidence heuristic need hardening before production use. No backtest or trading evidence presented.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Not adopted directly (no evidence, explicitly a prototype) - but the internal/external dual-timeframe structure classification is a more architecturally sound way to do what F57 attempted with a simple EMA proxy. Worth revisiting if F57's tooling issue ever gets resolved, as a 'do it properly' alternative rather than a new candidate on its own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dingo Optimization Algorithm (DOA)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MT5 Library</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Generic nature-inspired metaheuristic optimizer (part of a long-running population-optimization-algorithm comparison series), benchmarked on abstract math test functions - not trading-specific at all. DOA_dingo itself scored near the bottom of ~45 algorithms tested (0.2045), barely beating random walk (0.2194).</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rejected - no trading application, weak even on its own benchmark, and automated parameter-search tuning conflicts with the project's deliberate manual/OOS-gated ablation discipline (the whole reason E9_eur_tuned's overfit got caught was human-reviewed one-variable-at-a-time testing, not an automated optimizer).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Multi-Threaded Trading Robot with Machine Learning: From Concept to Implementation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MT5 Library</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Part 1 of a series reviving an old Python+MetaTrader5-hybrid ML trading system (Python does data/ML 'brains' via scikit-learn/XGBoost, MT5 Python API executes). Covers logging, data augmentation, feature engineering. Pure architecture/roadmap piece - explicitly 'first steps', ends with a wishlist (GPU clusters, GANs, 100-model ensembles) rather than any backtest or live results.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rejected for now - architecturally incompatible with WiseTrader's deliberate self-contained, restart-safe, single-MQL5-file design (an external live Python process is a different risk/ops profile entirely), and zero performance evidence exists in this installment to weigh against that cost anyway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Execution Cost and Slippage Sensitivity Analyzer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MT5 Library</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MQL5 script/tool (not a strategy) that reads closed-deal records and computes: breakeven cost per deal, 'cushion' (multiple of assumed real-world cost the edge survives before vanishing), profit factor at realistic cost, and win-erosion (winners that flip to losers under real spread/slippage/commission). Answers a genuinely different question than the project's existing OOS discipline: not 'does this generalize to new data' but 'how much of this edge is actually real once realistic costs are charged', which backtests systematically understate.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>F58</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Recommended - same category as F51 (validation tooling, not a trading signal, so no live-trading risk to weigh). Directly relevant: this project has repeatedly seen backtest-vs-demo gaps and the whole reason the demo forward-test exists is to catch exactly this kind of cost-reality gap; this tool could quantify A2_tuned's cost cushion NOW using data already sitting in the regression reports/journals, before the demo's own real number even arrives.</t>
         </is>
       </c>
     </row>
